--- a/architectures and decision enablers/architecture decision enabler/cloud-vendor-selection/Cloud_vendor_selection.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/cloud-vendor-selection/Cloud_vendor_selection.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\cloud-vendor-selection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\eBooks\Interview Quick Rampup\Fractional Architect Consulting &amp; Freelancing\UPWORK &amp; TOPMATE FILES AND PRODUCTS\CLOUD_VENDOR_SELECTION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5B0336F-EEEC-478E-87AC-31DF8BD3BCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD9C318-9697-46D2-8D64-E7AA133FA935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="dKKh4uMS4hAH1tCM60JuAo8eyVf+kCF8ToiPBotd0iUD7w7UOknvKm/UkrQu2m899UaQB9s1SE4olgdkkcckoA==" workbookSaltValue="psnyt9FPY/F+2bY/c/4s/w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5C6ED58D-5E8E-4A06-9B59-7556807F224B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5C6ED58D-5E8E-4A06-9B59-7556807F224B}"/>
   </bookViews>
   <sheets>
     <sheet name="Platform_DB" sheetId="1" r:id="rId1"/>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="122">
   <si>
     <t>Market Share &amp; Industry Presence</t>
   </si>
@@ -1461,6 +1462,9 @@
   </si>
   <si>
     <t>Vendor Scores</t>
+  </si>
+  <si>
+    <t>© 2026 Amit Kulkarni. All rights reserved.</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1474,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1516,6 +1520,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1546,7 +1558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1593,23 +1605,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1618,11 +1621,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1633,55 +1632,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFDCDFE5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFDCDFE5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -1696,6 +1711,7 @@
         <vertical/>
         <horizontal/>
       </border>
+      <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1709,32 +1725,7 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFDCDFE5"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFDCDFE5"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1795,6 +1786,9 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1812,25 +1806,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2492,11 +2467,68 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="medium">
           <color rgb="FFDCDFE5"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2724,7 +2756,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.59318181818181837</c:v>
+                  <c:v>0.59628571428571453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2854,7 +2886,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.58806818181818199</c:v>
+                  <c:v>0.59171428571428608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2984,7 +3016,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.59810606060606064</c:v>
+                  <c:v>0.60238095238095257</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3114,7 +3146,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.64356060606060617</c:v>
+                  <c:v>0.64866666666666684</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3244,7 +3276,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.68219696969696986</c:v>
+                  <c:v>0.67533333333333379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3374,7 +3406,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.70018939393939394</c:v>
+                  <c:v>0.70447619047619081</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4197,51 +4229,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{519A6EC5-5513-4B56-A1C4-49764987AF66}" name="Table1" displayName="Table1" ref="A1:V7" totalsRowShown="0" headerRowDxfId="10" dataDxfId="11" headerRowBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{519A6EC5-5513-4B56-A1C4-49764987AF66}" name="Table1" displayName="Table1" ref="A1:V7" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32">
   <autoFilter ref="A1:V7" xr:uid="{519A6EC5-5513-4B56-A1C4-49764987AF66}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{52DDB98B-E84C-4529-912B-820CAC7EC409}" name="Vendor Name " dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{338D0AD0-01C2-4F61-A82F-BDA2F6FDF138}" name="Market Share &amp; Industry Presence" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{C456307C-94FB-42EC-B1FC-AF4B4786BF4A}" name="Pricing Models &amp; Transparency" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{73B2E636-9EF9-4CA9-8C1D-BD41498871F2}" name="Global Data Center Footprint" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{F9C1CB30-9294-4E4F-8866-48A30A550714}" name="Compliance &amp; Security" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{FDB62100-4427-415E-A31E-CEB40E9057E4}" name="Hybrid Cloud Capabilities" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{34B93B9A-A078-4F04-B618-C48D6C417B42}" name="Enterprise Agreements &amp; Licensing Flexibilities" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{11E335C8-84A1-4A4E-B6BB-90FF88AB4A85}" name="DevOps Integration" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{FDCB189C-3A1D-47E7-BFA8-0B1FF5C5F196}" name="Global Network Infrastructure &amp; Performance" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{C1C45F28-C7B6-49FB-BF0E-FE8872E7DE52}" name="Latency, Throughput &amp; Scalability" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{04C55EF5-44C0-4741-BC8B-E1D0DD153772}" name="Failover &amp; High Availability" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{41CFA7E3-E291-40AD-AC5F-E1B50DB3798A}" name="Vendor Lock-in &amp; Portability" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{B82A32D1-AFB5-4556-AC9E-A60FC77B5ECB}" name="Management &amp; Monitoring Tools" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{DDB5373D-761D-446B-B8D6-245887174820}" name="Cost Management &amp; Optimization" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{FED075DC-C759-40FA-AE0E-82B74C6E27A4}" name="Storage Performance &amp; IOPS" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{3406619D-B978-4D13-91AA-A3445B1F541A}" name="Total Cost of Ownership (TCO) Analysis" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{34F4A3E9-10E4-4B1F-98FF-742B55093546}" name="Data Transfer &amp; Egress Cost" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{07F17B39-D511-46C3-AB59-3EBC24836705}" name="Network Security &amp; Firewalls" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{3BF90B0B-BCA2-4920-AEF1-A5A14E6387DC}" name="AI/ML Platform Capabilities" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{FA8CF6DB-C21B-4568-83B0-62531299E5A6}" name="Data Analytics &amp; Big Data" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{F3AC00CD-BEE2-47DE-A2DA-640037E71931}" name="Customer Support &amp; SLA Levels" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{C581A637-9415-40C6-B552-CE3701EC8BF2}" name="Developer Ecosystem &amp; Community" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{52DDB98B-E84C-4529-912B-820CAC7EC409}" name="Vendor Name " dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{338D0AD0-01C2-4F61-A82F-BDA2F6FDF138}" name="Market Share &amp; Industry Presence" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{C456307C-94FB-42EC-B1FC-AF4B4786BF4A}" name="Pricing Models &amp; Transparency" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{73B2E636-9EF9-4CA9-8C1D-BD41498871F2}" name="Global Data Center Footprint" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{F9C1CB30-9294-4E4F-8866-48A30A550714}" name="Compliance &amp; Security" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{FDB62100-4427-415E-A31E-CEB40E9057E4}" name="Hybrid Cloud Capabilities" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{34B93B9A-A078-4F04-B618-C48D6C417B42}" name="Enterprise Agreements &amp; Licensing Flexibilities" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{11E335C8-84A1-4A4E-B6BB-90FF88AB4A85}" name="DevOps Integration" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{FDCB189C-3A1D-47E7-BFA8-0B1FF5C5F196}" name="Global Network Infrastructure &amp; Performance" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{C1C45F28-C7B6-49FB-BF0E-FE8872E7DE52}" name="Latency, Throughput &amp; Scalability" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{04C55EF5-44C0-4741-BC8B-E1D0DD153772}" name="Failover &amp; High Availability" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{41CFA7E3-E291-40AD-AC5F-E1B50DB3798A}" name="Vendor Lock-in &amp; Portability" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{B82A32D1-AFB5-4556-AC9E-A60FC77B5ECB}" name="Management &amp; Monitoring Tools" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{DDB5373D-761D-446B-B8D6-245887174820}" name="Cost Management &amp; Optimization" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{FED075DC-C759-40FA-AE0E-82B74C6E27A4}" name="Storage Performance &amp; IOPS" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{3406619D-B978-4D13-91AA-A3445B1F541A}" name="Total Cost of Ownership (TCO) Analysis" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{34F4A3E9-10E4-4B1F-98FF-742B55093546}" name="Data Transfer &amp; Egress Cost" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{07F17B39-D511-46C3-AB59-3EBC24836705}" name="Network Security &amp; Firewalls" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{3BF90B0B-BCA2-4920-AEF1-A5A14E6387DC}" name="AI/ML Platform Capabilities" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{FA8CF6DB-C21B-4568-83B0-62531299E5A6}" name="Data Analytics &amp; Big Data" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{F3AC00CD-BEE2-47DE-A2DA-640037E71931}" name="Customer Support &amp; SLA Levels" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{C581A637-9415-40C6-B552-CE3701EC8BF2}" name="Developer Ecosystem &amp; Community" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{855343D0-2B4D-4664-BDE3-7AACF8D793AC}" name="Table2" displayName="Table2" ref="B1:H66" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{855343D0-2B4D-4664-BDE3-7AACF8D793AC}" name="Table2" displayName="Table2" ref="B1:H66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="B1:H66" xr:uid="{855343D0-2B4D-4664-BDE3-7AACF8D793AC}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A3F4D222-A543-4E50-8FC5-215D8D5274F3}" name="Category" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{1764FA2F-6467-4283-B72A-21106DF44EA2}" name="Client-Specific Question" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{44AE251D-0393-4D17-AF9A-AE091D884821}" name="User Priority" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{01705303-B046-489A-9514-FBC346C4B44F}" name="User Score" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{A3F4D222-A543-4E50-8FC5-215D8D5274F3}" name="Category" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{1764FA2F-6467-4283-B72A-21106DF44EA2}" name="Client-Specific Question" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{44AE251D-0393-4D17-AF9A-AE091D884821}" name="User Priority" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{01705303-B046-489A-9514-FBC346C4B44F}" name="User Score" dataDxfId="4">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(D2,"d",1,"c",0.75,"b",0.5,"a", 0.25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7E19D437-3C96-4EAC-8FEB-00D90359C53E}" name="Weight Priority_x000a_Low - 1 High - 5" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{BA6D474F-C865-4D2D-B02A-EE09FE49C122}" name="Client Target Scores" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{7E19D437-3C96-4EAC-8FEB-00D90359C53E}" name="Weight Priority_x000a_Low - 1 High - 5" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{BA6D474F-C865-4D2D-B02A-EE09FE49C122}" name="Client Target Scores" dataDxfId="3">
       <calculatedColumnFormula>AVERAGEIF(B$2:$B$66, B2, $E$2:$E$66)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{79E3DFE1-4A71-4D04-8894-1E8B4E59AF28}" name="Normalized Weight" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{79E3DFE1-4A71-4D04-8894-1E8B4E59AF28}" name="Normalized Weight" dataDxfId="2">
       <calculatedColumnFormula>SUMIF($B$2:$B$66, B2, $F$2:$F$66) / SUM(F$2:$F$66)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4250,7 +4282,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F2DD5FCE-25B2-428C-9CD0-527F85DB3CDA}" name="Table3" displayName="Table3" ref="A1:O28" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F2DD5FCE-25B2-428C-9CD0-527F85DB3CDA}" name="Table3" displayName="Table3" ref="A1:O28" totalsRowShown="0" headerRowDxfId="34">
   <autoFilter ref="A1:O28" xr:uid="{F2DD5FCE-25B2-428C-9CD0-527F85DB3CDA}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{984E4A1A-DE71-4FB2-BB0C-A5FE0359D57C}" name="Category"/>
@@ -4571,10 +4603,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3A4E66-2699-40DB-82A4-9EFD834BC6BA}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="1" max="1" width="42.88671875" customWidth="1"/>
     <col min="2" max="2" width="51.44140625" customWidth="1"/>
     <col min="3" max="3" width="45.109375" customWidth="1"/>
     <col min="4" max="4" width="38.77734375" customWidth="1"/>
@@ -5074,7 +5106,13 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="9" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="NbNlT2NyyVwRrTYF+vwGj8JW2AUL9QNnhAXkyeiZDQ8ji8usjIsavpIkUvK0Cq/hxeO2EeFDwBEZ5PkLnnQeUQ==" saltValue="ybqQ/Z9WswSnhdrL6sCo8Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -5085,12 +5123,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B89B61C-878D-4488-97B7-451CC195EEF8}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.21875" customWidth="1"/>
-    <col min="2" max="2" width="55.21875" customWidth="1"/>
-    <col min="3" max="3" width="76" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="48.77734375" customWidth="1"/>
+    <col min="3" max="3" width="69.88671875" customWidth="1"/>
     <col min="4" max="4" width="19.5546875" customWidth="1"/>
     <col min="5" max="5" width="16.44140625" customWidth="1"/>
     <col min="6" max="6" width="23.88671875" customWidth="1"/>
@@ -5120,7 +5158,7 @@
       <c r="G1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="18" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5134,23 +5172,23 @@
       <c r="C2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="16" cm="1">
+      <c r="D2" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="27" cm="1">
         <f t="array" ref="E2">_xlfn.SWITCH(D2,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2" s="34">
         <v>4</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="28">
         <f>AVERAGEIF(B$2:$B$66, B2, $E$2:$E$66)</f>
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="21">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H2" s="29">
         <f>SUMIF($B$2:$B$66, B2, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.1401869158878503E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
       <c r="I2" s="8"/>
     </row>
@@ -5164,23 +5202,23 @@
       <c r="C3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="16" cm="1">
+      <c r="E3" s="27" cm="1">
         <f t="array" ref="E3">_xlfn.SWITCH(D3,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="34">
         <v>4</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="28">
         <f>AVERAGEIF(B$2:$B$66, B3, $E$2:$E$66)</f>
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="21">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H3" s="29">
         <f>SUMIF($B$2:$B$66, B3, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.1401869158878503E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
       <c r="I3" s="8"/>
     </row>
@@ -5194,23 +5232,23 @@
       <c r="C4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="16" cm="1">
+      <c r="E4" s="27" cm="1">
         <f t="array" ref="E4">_xlfn.SWITCH(D4,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="16">
-        <v>4</v>
-      </c>
-      <c r="G4" s="19">
+      <c r="F4" s="34">
+        <v>3</v>
+      </c>
+      <c r="G4" s="28">
         <f>AVERAGEIF(B$2:$B$66, B4, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="29">
         <f>SUMIF($B$2:$B$66, B4, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.6074766355140186E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
       <c r="I4" s="8"/>
     </row>
@@ -5224,23 +5262,23 @@
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="16" cm="1">
+      <c r="E5" s="27" cm="1">
         <f t="array" ref="E5">_xlfn.SWITCH(D5,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="34">
         <v>3</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="28">
         <f>AVERAGEIF(B$2:$B$66, B5, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="29">
         <f>SUMIF($B$2:$B$66, B5, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.6074766355140186E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
       <c r="I5" s="8"/>
     </row>
@@ -5254,23 +5292,23 @@
       <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="16" cm="1">
+      <c r="E6" s="27" cm="1">
         <f t="array" ref="E6">_xlfn.SWITCH(D6,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="34">
         <v>4</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="28">
         <f>AVERAGEIF(B$2:$B$66, B6, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="29">
         <f>SUMIF($B$2:$B$66, B6, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.6074766355140186E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="I6" s="8"/>
     </row>
@@ -5284,23 +5322,23 @@
       <c r="C7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="16" cm="1">
+      <c r="E7" s="27" cm="1">
         <f t="array" ref="E7">_xlfn.SWITCH(D7,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="34">
         <v>5</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="28">
         <f>AVERAGEIF(B$2:$B$66, B7, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="29">
         <f>SUMIF($B$2:$B$66, B7, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.6074766355140186E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
       <c r="I7" s="8"/>
     </row>
@@ -5314,23 +5352,23 @@
       <c r="C8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="16" cm="1">
+      <c r="E8" s="27" cm="1">
         <f t="array" ref="E8">_xlfn.SWITCH(D8,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="34">
         <v>3</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="28">
         <f>AVERAGEIF(B$2:$B$66, B8, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="29">
         <f>SUMIF($B$2:$B$66, B8, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I8" s="8"/>
     </row>
@@ -5344,23 +5382,23 @@
       <c r="C9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="16" cm="1">
+      <c r="E9" s="27" cm="1">
         <f t="array" ref="E9">_xlfn.SWITCH(D9,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="34">
         <v>3</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="28">
         <f>AVERAGEIF(B$2:$B$66, B9, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="29">
         <f>SUMIF($B$2:$B$66, B9, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I9" s="8"/>
     </row>
@@ -5374,23 +5412,23 @@
       <c r="C10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="16" cm="1">
+      <c r="E10" s="27" cm="1">
         <f t="array" ref="E10">_xlfn.SWITCH(D10,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.75</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="34">
         <v>4</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="28">
         <f>AVERAGEIF(B$2:$B$66, B10, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="29">
         <f>SUMIF($B$2:$B$66, B10, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.2710280373831772E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
       <c r="I10" s="8"/>
     </row>
@@ -5404,23 +5442,23 @@
       <c r="C11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="16" cm="1">
+      <c r="E11" s="27" cm="1">
         <f t="array" ref="E11">_xlfn.SWITCH(D11,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="34">
         <v>3</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="28">
         <f>AVERAGEIF(B$2:$B$66, B11, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="29">
         <f>SUMIF($B$2:$B$66, B11, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.2710280373831772E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
       <c r="I11" s="8"/>
     </row>
@@ -5434,23 +5472,23 @@
       <c r="C12" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="16" cm="1">
+      <c r="E12" s="27" cm="1">
         <f t="array" ref="E12">_xlfn.SWITCH(D12,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="34">
         <v>4</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="28">
         <f>AVERAGEIF(B$2:$B$66, B12, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="29">
         <f>SUMIF($B$2:$B$66, B12, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I12" s="8"/>
     </row>
@@ -5464,23 +5502,23 @@
       <c r="C13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="16" cm="1">
+      <c r="E13" s="27" cm="1">
         <f t="array" ref="E13">_xlfn.SWITCH(D13,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.75</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="34">
         <v>3</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="28">
         <f>AVERAGEIF(B$2:$B$66, B13, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="29">
         <f>SUMIF($B$2:$B$66, B13, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I13" s="8"/>
     </row>
@@ -5494,23 +5532,23 @@
       <c r="C14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="16" cm="1">
+      <c r="E14" s="27" cm="1">
         <f t="array" ref="E14">_xlfn.SWITCH(D14,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.25</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="34">
         <v>2</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="28">
         <f>AVERAGEIF(B$2:$B$66, B14, $E$2:$E$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="29">
         <f>SUMIF($B$2:$B$66, B14, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I14" s="8"/>
     </row>
@@ -5524,23 +5562,23 @@
       <c r="C15" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="16" cm="1">
+      <c r="E15" s="27" cm="1">
         <f t="array" ref="E15">_xlfn.SWITCH(D15,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="34">
         <v>5</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="28">
         <f>AVERAGEIF(B$2:$B$66, B15, $E$2:$E$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="29">
         <f>SUMIF($B$2:$B$66, B15, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -5554,23 +5592,23 @@
       <c r="C16" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="16" cm="1">
+      <c r="E16" s="27" cm="1">
         <f t="array" ref="E16">_xlfn.SWITCH(D16,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="34">
         <v>3</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="28">
         <f>AVERAGEIF(B$2:$B$66, B16, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="29">
         <f>SUMIF($B$2:$B$66, B16, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I16" s="8"/>
     </row>
@@ -5584,23 +5622,23 @@
       <c r="C17" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="16" cm="1">
+      <c r="E17" s="27" cm="1">
         <f t="array" ref="E17">_xlfn.SWITCH(D17,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="34">
         <v>4</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="28">
         <f>AVERAGEIF(B$2:$B$66, B17, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="29">
         <f>SUMIF($B$2:$B$66, B17, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I17" s="8"/>
     </row>
@@ -5614,23 +5652,23 @@
       <c r="C18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="16" cm="1">
+      <c r="E18" s="27" cm="1">
         <f t="array" ref="E18">_xlfn.SWITCH(D18,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="34">
         <v>1</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="28">
         <f>AVERAGEIF(B$2:$B$66, B18, $E$2:$E$66)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="29">
         <f>SUMIF($B$2:$B$66, B18, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.7383177570093455E-2</v>
+        <v>3.7558685446009391E-2</v>
       </c>
       <c r="I18" s="8"/>
     </row>
@@ -5644,23 +5682,23 @@
       <c r="C19" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="16" cm="1">
+      <c r="E19" s="27" cm="1">
         <f t="array" ref="E19">_xlfn.SWITCH(D19,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="34">
         <v>4</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="28">
         <f>AVERAGEIF(B$2:$B$66, B19, $E$2:$E$66)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="29">
         <f>SUMIF($B$2:$B$66, B19, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.7383177570093455E-2</v>
+        <v>3.7558685446009391E-2</v>
       </c>
       <c r="I19" s="8"/>
     </row>
@@ -5674,23 +5712,23 @@
       <c r="C20" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="16" cm="1">
+      <c r="E20" s="27" cm="1">
         <f t="array" ref="E20">_xlfn.SWITCH(D20,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="34">
         <v>2</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="28">
         <f>AVERAGEIF(B$2:$B$66, B20, $E$2:$E$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="29">
         <f>SUMIF($B$2:$B$66, B20, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I20" s="8"/>
     </row>
@@ -5704,23 +5742,23 @@
       <c r="C21" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="16" cm="1">
+      <c r="E21" s="27" cm="1">
         <f t="array" ref="E21">_xlfn.SWITCH(D21,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.75</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="34">
         <v>5</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="28">
         <f>AVERAGEIF(B$2:$B$66, B21, $E$2:$E$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="29">
         <f>SUMIF($B$2:$B$66, B21, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
       <c r="I21" s="8"/>
     </row>
@@ -5734,23 +5772,23 @@
       <c r="C22" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="16" cm="1">
+      <c r="E22" s="27" cm="1">
         <f t="array" ref="E22">_xlfn.SWITCH(D22,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="34">
         <v>5</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="28">
         <f>AVERAGEIF(B$2:$B$66, B22, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="29">
         <f>SUMIF($B$2:$B$66, B22, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>6.0747663551401869E-2</v>
+        <v>6.1032863849765258E-2</v>
       </c>
       <c r="I22" s="8"/>
     </row>
@@ -5764,23 +5802,23 @@
       <c r="C23" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="16" cm="1">
+      <c r="E23" s="27" cm="1">
         <f t="array" ref="E23">_xlfn.SWITCH(D23,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="34">
         <v>3</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="28">
         <f>AVERAGEIF(B$2:$B$66, B23, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="29">
         <f>SUMIF($B$2:$B$66, B23, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>6.0747663551401869E-2</v>
+        <v>6.1032863849765258E-2</v>
       </c>
       <c r="I23" s="8"/>
     </row>
@@ -5794,23 +5832,23 @@
       <c r="C24" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="16" cm="1">
+      <c r="E24" s="27" cm="1">
         <f t="array" ref="E24">_xlfn.SWITCH(D24,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="34">
         <v>4</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="28">
         <f>AVERAGEIF(B$2:$B$66, B24, $E$2:$E$66)</f>
         <v>1</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="29">
         <f>SUMIF($B$2:$B$66, B24, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.7383177570093455E-2</v>
+        <v>3.7558685446009391E-2</v>
       </c>
       <c r="I24" s="8"/>
     </row>
@@ -5824,23 +5862,23 @@
       <c r="C25" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="16" cm="1">
+      <c r="E25" s="27" cm="1">
         <f t="array" ref="E25">_xlfn.SWITCH(D25,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="34">
         <v>4</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="28">
         <f>AVERAGEIF(B$2:$B$66, B25, $E$2:$E$66)</f>
         <v>1</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="29">
         <f>SUMIF($B$2:$B$66, B25, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.7383177570093455E-2</v>
+        <v>3.7558685446009391E-2</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -5854,23 +5892,23 @@
       <c r="C26" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="16" cm="1">
+      <c r="E26" s="27" cm="1">
         <f t="array" ref="E26">_xlfn.SWITCH(D26,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="34">
         <v>5</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="28">
         <f>AVERAGEIF(B$2:$B$66, B26, $E$2:$E$66)</f>
         <v>1</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="29">
         <f>SUMIF($B$2:$B$66, B26, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.2710280373831772E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
       <c r="I26" s="8"/>
     </row>
@@ -5884,23 +5922,23 @@
       <c r="C27" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="16" cm="1">
+      <c r="E27" s="27" cm="1">
         <f t="array" ref="E27">_xlfn.SWITCH(D27,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="34">
         <v>2</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="28">
         <f>AVERAGEIF(B$2:$B$66, B27, $E$2:$E$66)</f>
         <v>1</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="29">
         <f>SUMIF($B$2:$B$66, B27, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.2710280373831772E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
       <c r="I27" s="8"/>
     </row>
@@ -5914,23 +5952,23 @@
       <c r="C28" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="16" cm="1">
+      <c r="E28" s="27" cm="1">
         <f t="array" ref="E28">_xlfn.SWITCH(D28,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="34">
         <v>1</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="28">
         <f>AVERAGEIF(B$2:$B$66, B28, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="29">
         <f>SUMIF($B$2:$B$66, B28, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>9.3457943925233638E-3</v>
+        <v>9.3896713615023476E-3</v>
       </c>
       <c r="I28" s="8"/>
     </row>
@@ -5944,23 +5982,23 @@
       <c r="C29" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="16" cm="1">
+      <c r="E29" s="27" cm="1">
         <f t="array" ref="E29">_xlfn.SWITCH(D29,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="34">
         <v>1</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="28">
         <f>AVERAGEIF(B$2:$B$66, B29, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="29">
         <f>SUMIF($B$2:$B$66, B29, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>9.3457943925233638E-3</v>
+        <v>9.3896713615023476E-3</v>
       </c>
       <c r="I29" s="8"/>
     </row>
@@ -5974,23 +6012,23 @@
       <c r="C30" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="16" cm="1">
+      <c r="E30" s="27" cm="1">
         <f t="array" ref="E30">_xlfn.SWITCH(D30,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="34">
         <v>4</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="28">
         <f>AVERAGEIF(B$2:$B$66, B30, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="29">
         <f>SUMIF($B$2:$B$66, B30, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I30" s="8"/>
     </row>
@@ -6004,23 +6042,23 @@
       <c r="C31" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="16" cm="1">
+      <c r="E31" s="27" cm="1">
         <f t="array" ref="E31">_xlfn.SWITCH(D31,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="34">
         <v>5</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="28">
         <f>AVERAGEIF(B$2:$B$66, B31, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="29">
         <f>SUMIF($B$2:$B$66, B31, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I31" s="8"/>
     </row>
@@ -6034,23 +6072,23 @@
       <c r="C32" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="16" cm="1">
+      <c r="E32" s="27" cm="1">
         <f t="array" ref="E32">_xlfn.SWITCH(D32,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="34">
         <v>2</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="28">
         <f>AVERAGEIF(B$2:$B$66, B32, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H32" s="21">
+      <c r="H32" s="29">
         <f>SUMIF($B$2:$B$66, B32, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.336448598130841E-2</v>
+        <v>2.3474178403755867E-2</v>
       </c>
       <c r="I32" s="8"/>
     </row>
@@ -6064,23 +6102,23 @@
       <c r="C33" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="16" cm="1">
+      <c r="E33" s="27" cm="1">
         <f t="array" ref="E33">_xlfn.SWITCH(D33,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="34">
         <v>3</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="28">
         <f>AVERAGEIF(B$2:$B$66, B33, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="29">
         <f>SUMIF($B$2:$B$66, B33, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.336448598130841E-2</v>
+        <v>2.3474178403755867E-2</v>
       </c>
       <c r="I33" s="8"/>
     </row>
@@ -6094,23 +6132,23 @@
       <c r="C34" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="16" cm="1">
+      <c r="E34" s="27" cm="1">
         <f t="array" ref="E34">_xlfn.SWITCH(D34,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="34">
         <v>4</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="28">
         <f>AVERAGEIF(B$2:$B$66, B34, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H34" s="21">
+      <c r="H34" s="29">
         <f>SUMIF($B$2:$B$66, B34, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I34" s="8"/>
     </row>
@@ -6124,23 +6162,23 @@
       <c r="C35" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="16" cm="1">
+      <c r="E35" s="27" cm="1">
         <f t="array" ref="E35">_xlfn.SWITCH(D35,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="34">
         <v>5</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="28">
         <f>AVERAGEIF(B$2:$B$66, B35, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="29">
         <f>SUMIF($B$2:$B$66, B35, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I35" s="8"/>
     </row>
@@ -6154,23 +6192,23 @@
       <c r="C36" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="16" cm="1">
+      <c r="E36" s="27" cm="1">
         <f t="array" ref="E36">_xlfn.SWITCH(D36,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="34">
         <v>4</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="28">
         <f>AVERAGEIF(B$2:$B$66, B36, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="29">
         <f>SUMIF($B$2:$B$66, B36, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.2710280373831772E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
       <c r="I36" s="8"/>
     </row>
@@ -6184,23 +6222,23 @@
       <c r="C37" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="16" cm="1">
+      <c r="E37" s="27" cm="1">
         <f t="array" ref="E37">_xlfn.SWITCH(D37,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="34">
         <v>3</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="28">
         <f>AVERAGEIF(B$2:$B$66, B37, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="29">
         <f>SUMIF($B$2:$B$66, B37, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.2710280373831772E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
       <c r="I37" s="8"/>
     </row>
@@ -6214,23 +6252,23 @@
       <c r="C38" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="16" cm="1">
+      <c r="E38" s="27" cm="1">
         <f t="array" ref="E38">_xlfn.SWITCH(D38,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="34">
         <v>2</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="28">
         <f>AVERAGEIF(B$2:$B$66, B38, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="29">
         <f>SUMIF($B$2:$B$66, B38, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>1.4018691588785047E-2</v>
+        <v>1.4084507042253521E-2</v>
       </c>
       <c r="I38" s="8"/>
     </row>
@@ -6244,23 +6282,23 @@
       <c r="C39" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="16" cm="1">
+      <c r="E39" s="27" cm="1">
         <f t="array" ref="E39">_xlfn.SWITCH(D39,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="34">
         <v>1</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="28">
         <f>AVERAGEIF(B$2:$B$66, B39, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="29">
         <f>SUMIF($B$2:$B$66, B39, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>1.4018691588785047E-2</v>
+        <v>1.4084507042253521E-2</v>
       </c>
       <c r="I39" s="8"/>
     </row>
@@ -6274,23 +6312,23 @@
       <c r="C40" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E40" s="16" cm="1">
+      <c r="E40" s="27" cm="1">
         <f t="array" ref="E40">_xlfn.SWITCH(D40,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="34">
         <v>2</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="28">
         <f>AVERAGEIF(B$2:$B$66, B40, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="29">
         <f>SUMIF($B$2:$B$66, B40, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.336448598130841E-2</v>
+        <v>2.3474178403755867E-2</v>
       </c>
       <c r="I40" s="8"/>
     </row>
@@ -6304,23 +6342,23 @@
       <c r="C41" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="16" cm="1">
+      <c r="E41" s="27" cm="1">
         <f t="array" ref="E41">_xlfn.SWITCH(D41,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="34">
         <v>3</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="28">
         <f>AVERAGEIF(B$2:$B$66, B41, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="29">
         <f>SUMIF($B$2:$B$66, B41, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.336448598130841E-2</v>
+        <v>2.3474178403755867E-2</v>
       </c>
       <c r="I41" s="8"/>
     </row>
@@ -6334,23 +6372,23 @@
       <c r="C42" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E42" s="16" cm="1">
+      <c r="E42" s="27" cm="1">
         <f t="array" ref="E42">_xlfn.SWITCH(D42,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="34">
         <v>4</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="28">
         <f>AVERAGEIF(B$2:$B$66, B42, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="29">
         <f>SUMIF($B$2:$B$66, B42, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I42" s="8"/>
     </row>
@@ -6364,23 +6402,23 @@
       <c r="C43" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="16" cm="1">
+      <c r="E43" s="27" cm="1">
         <f t="array" ref="E43">_xlfn.SWITCH(D43,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="34">
         <v>5</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="28">
         <f>AVERAGEIF(B$2:$B$66, B43, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="29">
         <f>SUMIF($B$2:$B$66, B43, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="I43" s="8"/>
     </row>
@@ -6394,23 +6432,23 @@
       <c r="C44" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="16" cm="1">
+      <c r="E44" s="27" cm="1">
         <f t="array" ref="E44">_xlfn.SWITCH(D44,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="34">
         <v>4</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="28">
         <f>AVERAGEIF(B$2:$B$66, B44, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H44" s="21">
+      <c r="H44" s="29">
         <f>SUMIF($B$2:$B$66, B44, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>1.8691588785046728E-2</v>
+        <v>1.8779342723004695E-2</v>
       </c>
       <c r="I44" s="8"/>
     </row>
@@ -6424,23 +6462,23 @@
       <c r="C45" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="16" cm="1">
+      <c r="E45" s="27" cm="1">
         <f t="array" ref="E45">_xlfn.SWITCH(D45,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="34">
         <v>2</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="28">
         <f>AVERAGEIF(B$2:$B$66, B45, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H45" s="21">
+      <c r="H45" s="29">
         <f>SUMIF($B$2:$B$66, B45, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>9.3457943925233638E-3</v>
+        <v>9.3896713615023476E-3</v>
       </c>
       <c r="I45" s="8"/>
     </row>
@@ -6454,23 +6492,23 @@
       <c r="C46" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="16" cm="1">
+      <c r="E46" s="27" cm="1">
         <f t="array" ref="E46">_xlfn.SWITCH(D46,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="34">
         <v>5</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="28">
         <f>AVERAGEIF(B$2:$B$66, B46, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H46" s="21">
+      <c r="H46" s="29">
         <f>SUMIF($B$2:$B$66, B46, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.336448598130841E-2</v>
+        <v>2.3474178403755867E-2</v>
       </c>
       <c r="I46" s="8"/>
     </row>
@@ -6484,23 +6522,23 @@
       <c r="C47" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E47" s="16" cm="1">
+      <c r="E47" s="27" cm="1">
         <f t="array" ref="E47">_xlfn.SWITCH(D47,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="34">
         <v>1</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="28">
         <f>AVERAGEIF(B$2:$B$66, B47, $E$2:$E$66)</f>
         <v>0.875</v>
       </c>
-      <c r="H47" s="21">
+      <c r="H47" s="29">
         <f>SUMIF($B$2:$B$66, B47, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>1.4018691588785047E-2</v>
+        <v>1.4084507042253521E-2</v>
       </c>
       <c r="I47" s="8"/>
     </row>
@@ -6514,23 +6552,23 @@
       <c r="C48" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E48" s="16" cm="1">
+      <c r="E48" s="27" cm="1">
         <f t="array" ref="E48">_xlfn.SWITCH(D48,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.75</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="34">
         <v>2</v>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="28">
         <f>AVERAGEIF(B$2:$B$66, B48, $E$2:$E$66)</f>
         <v>0.875</v>
       </c>
-      <c r="H48" s="21">
+      <c r="H48" s="29">
         <f>SUMIF($B$2:$B$66, B48, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>1.4018691588785047E-2</v>
+        <v>1.4084507042253521E-2</v>
       </c>
       <c r="I48" s="8"/>
     </row>
@@ -6541,26 +6579,26 @@
       <c r="B49" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E49" s="16" cm="1">
+      <c r="E49" s="27" cm="1">
         <f t="array" ref="E49">_xlfn.SWITCH(D49,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.75</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="34">
         <v>3</v>
       </c>
-      <c r="G49" s="19">
+      <c r="G49" s="28">
         <f>AVERAGEIF(B$2:$B$66, B49, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H49" s="21">
+      <c r="H49" s="29">
         <f>SUMIF($B$2:$B$66, B49, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="141" thickBot="1" x14ac:dyDescent="0.35">
@@ -6570,26 +6608,26 @@
       <c r="B50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E50" s="16" cm="1">
+      <c r="E50" s="27" cm="1">
         <f t="array" ref="E50">_xlfn.SWITCH(D50,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>1</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="34">
         <v>3</v>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="28">
         <f>AVERAGEIF(B$2:$B$66, B50, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H50" s="21">
+      <c r="H50" s="29">
         <f>SUMIF($B$2:$B$66, B50, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="141" thickBot="1" x14ac:dyDescent="0.35">
@@ -6599,26 +6637,26 @@
       <c r="B51" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="16" cm="1">
+      <c r="E51" s="27" cm="1">
         <f t="array" ref="E51">_xlfn.SWITCH(D51,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="34">
         <v>3</v>
       </c>
-      <c r="G51" s="19">
+      <c r="G51" s="28">
         <f>AVERAGEIF(B$2:$B$66, B51, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H51" s="21">
+      <c r="H51" s="29">
         <f>SUMIF($B$2:$B$66, B51, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -6628,26 +6666,26 @@
       <c r="B52" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="16" cm="1">
+      <c r="E52" s="27" cm="1">
         <f t="array" ref="E52">_xlfn.SWITCH(D52,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="34">
         <v>3</v>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="28">
         <f>AVERAGEIF(B$2:$B$66, B52, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H52" s="21">
+      <c r="H52" s="29">
         <f>SUMIF($B$2:$B$66, B52, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.8037383177570093E-2</v>
+        <v>2.8169014084507043E-2</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -6657,26 +6695,26 @@
       <c r="B53" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E53" s="16" cm="1">
+      <c r="E53" s="27" cm="1">
         <f t="array" ref="E53">_xlfn.SWITCH(D53,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="34">
         <v>3</v>
       </c>
-      <c r="G53" s="19">
+      <c r="G53" s="28">
         <f>AVERAGEIF(B$2:$B$66, B53, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H53" s="21">
+      <c r="H53" s="29">
         <f>SUMIF($B$2:$B$66, B53, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.8037383177570093E-2</v>
+        <v>2.8169014084507043E-2</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -6686,26 +6724,26 @@
       <c r="B54" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D54" s="16" t="s">
+      <c r="D54" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="16" cm="1">
+      <c r="E54" s="27" cm="1">
         <f t="array" ref="E54">_xlfn.SWITCH(D54,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="34">
         <v>3</v>
       </c>
-      <c r="G54" s="19">
+      <c r="G54" s="28">
         <f>AVERAGEIF(B$2:$B$66, B54, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H54" s="21">
+      <c r="H54" s="29">
         <f>SUMIF($B$2:$B$66, B54, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.8037383177570093E-2</v>
+        <v>2.8169014084507043E-2</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -6715,26 +6753,26 @@
       <c r="B55" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E55" s="16" cm="1">
+      <c r="E55" s="27" cm="1">
         <f t="array" ref="E55">_xlfn.SWITCH(D55,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="34">
         <v>3</v>
       </c>
-      <c r="G55" s="19">
+      <c r="G55" s="28">
         <f>AVERAGEIF(B$2:$B$66, B55, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H55" s="21">
+      <c r="H55" s="29">
         <f>SUMIF($B$2:$B$66, B55, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>2.8037383177570093E-2</v>
+        <v>2.8169014084507043E-2</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="141" thickBot="1" x14ac:dyDescent="0.35">
@@ -6744,26 +6782,26 @@
       <c r="B56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E56" s="16" cm="1">
+      <c r="E56" s="27" cm="1">
         <f t="array" ref="E56">_xlfn.SWITCH(D56,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="34">
         <v>3</v>
       </c>
-      <c r="G56" s="19">
+      <c r="G56" s="28">
         <f>AVERAGEIF(B$2:$B$66, B56, $E$2:$E$66)</f>
-        <v>0.5</v>
-      </c>
-      <c r="H56" s="21">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H56" s="29">
         <f>SUMIF($B$2:$B$66, B56, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.1401869158878503E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -6773,26 +6811,26 @@
       <c r="B57" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E57" s="16" cm="1">
+      <c r="E57" s="27" cm="1">
         <f t="array" ref="E57">_xlfn.SWITCH(D57,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="34">
         <v>5</v>
       </c>
-      <c r="G57" s="19">
+      <c r="G57" s="28">
         <f>AVERAGEIF(B$2:$B$66, B57, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H57" s="21">
+      <c r="H57" s="29">
         <f>SUMIF($B$2:$B$66, B57, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.6074766355140186E-2</v>
+        <v>5.1643192488262914E-2</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -6802,26 +6840,26 @@
       <c r="B58" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D58" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E58" s="16" cm="1">
+      <c r="E58" s="27" cm="1">
         <f t="array" ref="E58">_xlfn.SWITCH(D58,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="34">
         <v>3</v>
       </c>
-      <c r="G58" s="19">
+      <c r="G58" s="28">
         <f>AVERAGEIF(B$2:$B$66, B58, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H58" s="21">
+      <c r="H58" s="29">
         <f>SUMIF($B$2:$B$66, B58, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>5.6074766355140186E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="141" thickBot="1" x14ac:dyDescent="0.35">
@@ -6831,26 +6869,26 @@
       <c r="B59" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="16" t="s">
+      <c r="D59" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E59" s="16" cm="1">
+      <c r="E59" s="27" cm="1">
         <f t="array" ref="E59">_xlfn.SWITCH(D59,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="34">
         <v>3</v>
       </c>
-      <c r="G59" s="19">
+      <c r="G59" s="28">
         <f>AVERAGEIF(B$2:$B$66, B59, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H59" s="21">
+      <c r="H59" s="29">
         <f>SUMIF($B$2:$B$66, B59, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.2056074766355138E-2</v>
+        <v>4.2253521126760563E-2</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="141" thickBot="1" x14ac:dyDescent="0.35">
@@ -6860,26 +6898,26 @@
       <c r="B60" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="16" cm="1">
+      <c r="E60" s="27" cm="1">
         <f t="array" ref="E60">_xlfn.SWITCH(D60,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="34">
         <v>3</v>
       </c>
-      <c r="G60" s="19">
+      <c r="G60" s="28">
         <f>AVERAGEIF(B$2:$B$66, B60, $E$2:$E$66)</f>
         <v>0.75</v>
       </c>
-      <c r="H60" s="21">
+      <c r="H60" s="29">
         <f>SUMIF($B$2:$B$66, B60, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -6889,26 +6927,26 @@
       <c r="B61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E61" s="16" cm="1">
+      <c r="E61" s="27" cm="1">
         <f t="array" ref="E61">_xlfn.SWITCH(D61,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="34">
         <v>3</v>
       </c>
-      <c r="G61" s="19">
+      <c r="G61" s="28">
         <f>AVERAGEIF(B$2:$B$66, B61, $E$2:$E$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="H61" s="21">
+      <c r="H61" s="29">
         <f>SUMIF($B$2:$B$66, B61, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -6918,26 +6956,26 @@
       <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D62" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E62" s="16" cm="1">
+      <c r="E62" s="27" cm="1">
         <f t="array" ref="E62">_xlfn.SWITCH(D62,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="34">
         <v>3</v>
       </c>
-      <c r="G62" s="19">
+      <c r="G62" s="28">
         <f>AVERAGEIF(B$2:$B$66, B62, $E$2:$E$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="29">
         <f>SUMIF($B$2:$B$66, B62, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,26 +6985,26 @@
       <c r="B63" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D63" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E63" s="16" cm="1">
+      <c r="E63" s="27" cm="1">
         <f t="array" ref="E63">_xlfn.SWITCH(D63,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="34">
         <v>3</v>
       </c>
-      <c r="G63" s="19">
+      <c r="G63" s="28">
         <f>AVERAGEIF(B$2:$B$66, B63, $E$2:$E$66)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H63" s="21">
+      <c r="H63" s="29">
         <f>SUMIF($B$2:$B$66, B63, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>3.7383177570093455E-2</v>
+        <v>3.7558685446009391E-2</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -6976,26 +7014,26 @@
       <c r="B64" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E64" s="16" cm="1">
+      <c r="E64" s="27" cm="1">
         <f t="array" ref="E64">_xlfn.SWITCH(D64,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="34">
         <v>3</v>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="28">
         <f>AVERAGEIF(B$2:$B$66, B64, $E$2:$E$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="H64" s="21">
+      <c r="H64" s="29">
         <f>SUMIF($B$2:$B$66, B64, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>4.6728971962616821E-2</v>
+        <v>4.6948356807511735E-2</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -7005,26 +7043,26 @@
       <c r="B65" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E65" s="16" cm="1">
+      <c r="E65" s="27" cm="1">
         <f t="array" ref="E65">_xlfn.SWITCH(D65,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="34">
         <v>5</v>
       </c>
-      <c r="G65" s="19">
+      <c r="G65" s="28">
         <f>AVERAGEIF(B$2:$B$66, B65, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H65" s="21">
+      <c r="H65" s="29">
         <f>SUMIF($B$2:$B$66, B65, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>6.0747663551401869E-2</v>
+        <v>6.1032863849765258E-2</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -7034,29 +7072,35 @@
       <c r="B66" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E66" s="16" cm="1">
+      <c r="E66" s="27" cm="1">
         <f t="array" ref="E66">_xlfn.SWITCH(D66,"d",1,"c",0.75,"b",0.5,"a", 0.25)</f>
         <v>0.5</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="34">
         <v>3</v>
       </c>
-      <c r="G66" s="19">
+      <c r="G66" s="28">
         <f>AVERAGEIF(B$2:$B$66, B66, $E$2:$E$66)</f>
         <v>0.5</v>
       </c>
-      <c r="H66" s="21">
+      <c r="H66" s="29">
         <f>SUMIF($B$2:$B$66, B66, $F$2:$F$66) / SUM(F$2:$F$66)</f>
-        <v>1.4018691588785047E-2</v>
+        <v>1.4084507042253521E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B68" s="33" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="vbmUjodeeXougOlqfo2IXUlmRcK0GiA56JV4AuPcrsydkHQceEHvHE86/MnCvhqjbWuk7kK5CBblGy7x0dRVqQ==" saltValue="4aNnyAOxLrOBgOfkf8x0MA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Organizational Input" prompt="Select one from 4 options a,b,c,d" sqref="D2:D66" xr:uid="{53ADDEB5-1C5C-4E9E-9EBC-4222AF262646}">
       <formula1>"a,b,c,d"</formula1>
@@ -7074,7 +7118,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDB065F-3BD3-472D-887F-B8D6140A877C}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.109375" customWidth="1"/>
@@ -7094,1392 +7138,1398 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="19" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A2, User_Responses!$G$2:$G$66)</f>
-        <v>0.5</v>
-      </c>
-      <c r="C2" s="25">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C2" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A2, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>6.2500000000000014E-2</v>
-      </c>
-      <c r="D2" s="25">
+        <v>6.2857142857142903E-2</v>
+      </c>
+      <c r="D2" s="30">
         <f>_xlfn.XLOOKUP(A2, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="31">
         <f>1-ABS(B2-D2)</f>
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="25">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2" s="30">
         <f>_xlfn.XLOOKUP(A2, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="30">
         <f>1-ABS(B2-F2)</f>
-        <v>0.6</v>
-      </c>
-      <c r="H2" s="25">
+        <v>0.68333333333333335</v>
+      </c>
+      <c r="H2" s="30">
         <f>_xlfn.XLOOKUP(A2, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="30">
         <f>1-ABS(B2-H2)</f>
-        <v>0.7</v>
-      </c>
-      <c r="J2" s="25">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="J2" s="30">
         <f>_xlfn.XLOOKUP(A2, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.6</v>
       </c>
-      <c r="K2" s="25">
+      <c r="K2" s="30">
         <f>1-ABS(B2-J2)</f>
-        <v>0.9</v>
-      </c>
-      <c r="L2" s="25">
+        <v>0.98333333333333339</v>
+      </c>
+      <c r="L2" s="30">
         <f>_xlfn.XLOOKUP(A2, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.5</v>
       </c>
-      <c r="M2" s="25">
+      <c r="M2" s="30">
         <f>1-ABS(B2-L2)</f>
-        <v>1</v>
-      </c>
-      <c r="N2" s="25">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="N2" s="30">
         <f>_xlfn.XLOOKUP(A2, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.6</v>
       </c>
-      <c r="O2" s="25">
+      <c r="O2" s="30">
         <f>1-ABS(B2-N2)</f>
-        <v>0.9</v>
+        <v>0.98333333333333339</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A3, User_Responses!$G$2:$G$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A3, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>6.8181818181818191E-2</v>
-      </c>
-      <c r="D3" s="25">
+        <v>6.2857142857142903E-2</v>
+      </c>
+      <c r="D3" s="30">
         <f>_xlfn.XLOOKUP(A3, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.7</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="31">
         <f t="shared" ref="E3:E22" si="0">1-ABS(B3-D3)</f>
         <v>0.96666666666666667</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="30">
         <f>_xlfn.XLOOKUP(A3, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.8</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="30">
         <f t="shared" ref="G3:G22" si="1">1-ABS(B3-F3)</f>
         <v>0.86666666666666659</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="30">
         <f>_xlfn.XLOOKUP(A3, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.9</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="30">
         <f t="shared" ref="I3:I22" si="2">1-ABS(B3-H3)</f>
         <v>0.76666666666666661</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="30">
         <f>_xlfn.XLOOKUP(A3, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>1</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="30">
         <f t="shared" ref="K3:K22" si="3">1-ABS(B3-J3)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="30">
         <f>_xlfn.XLOOKUP(A3, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="30">
         <f t="shared" ref="M3:M22" si="4">1-ABS(B3-L3)</f>
         <v>0.96666666666666667</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="30">
         <f>_xlfn.XLOOKUP(A3, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="30">
         <f t="shared" ref="O3:O22" si="5">1-ABS(B3-N3)</f>
         <v>0.86666666666666659</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A4, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A4, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>6.8181818181818191E-2</v>
-      </c>
-      <c r="D4" s="25">
+        <v>6.8571428571428616E-2</v>
+      </c>
+      <c r="D4" s="30">
         <f>_xlfn.XLOOKUP(A4, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="31">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="30">
         <f>_xlfn.XLOOKUP(A4, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="30">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="30">
         <f>_xlfn.XLOOKUP(A4, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="30">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="30">
         <f>_xlfn.XLOOKUP(A4, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="30">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="30">
         <f>_xlfn.XLOOKUP(A4, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="30">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="N4" s="25">
+      <c r="N4" s="30">
         <f>_xlfn.XLOOKUP(A4, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="30">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A5, User_Responses!$G$2:$G$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A5, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>5.1136363636363646E-2</v>
-      </c>
-      <c r="D5" s="25">
+        <v>5.1428571428571462E-2</v>
+      </c>
+      <c r="D5" s="30">
         <f>_xlfn.XLOOKUP(A5, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="31">
         <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="30">
         <f>_xlfn.XLOOKUP(A5, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>1</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="30">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="30">
         <f>_xlfn.XLOOKUP(A5, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.9</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="30">
         <f t="shared" si="2"/>
         <v>0.76666666666666661</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="30">
         <f>_xlfn.XLOOKUP(A5, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.9</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="30">
         <f t="shared" si="3"/>
         <v>0.76666666666666661</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="30">
         <f>_xlfn.XLOOKUP(A5, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>1</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="30">
         <f t="shared" si="4"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="30">
         <f>_xlfn.XLOOKUP(A5, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="30">
         <f t="shared" si="5"/>
         <v>0.96666666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A6, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A6, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>2.6515151515151519E-2</v>
-      </c>
-      <c r="D6" s="25">
+        <v>2.6666666666666686E-2</v>
+      </c>
+      <c r="D6" s="30">
         <f>_xlfn.XLOOKUP(A6, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.8</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="31">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="30">
         <f>_xlfn.XLOOKUP(A6, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="30">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="30">
         <f>_xlfn.XLOOKUP(A6, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="30">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="30">
         <f>_xlfn.XLOOKUP(A6, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="30">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="30">
         <f>_xlfn.XLOOKUP(A6, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.9</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="30">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="30">
         <f>_xlfn.XLOOKUP(A6, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="30">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A7, User_Responses!$G$2:$G$66)</f>
         <v>0.75</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A7, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>5.681818181818183E-2</v>
-      </c>
-      <c r="D7" s="25">
+        <v>5.7142857142857169E-2</v>
+      </c>
+      <c r="D7" s="30">
         <f>_xlfn.XLOOKUP(A7, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.7</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="31">
         <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="30">
         <f>_xlfn.XLOOKUP(A7, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>1</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="30">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="30">
         <f>_xlfn.XLOOKUP(A7, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="30">
         <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="30">
         <f>_xlfn.XLOOKUP(A7, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.9</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="30">
         <f t="shared" si="3"/>
         <v>0.85</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="30">
         <f>_xlfn.XLOOKUP(A7, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.8</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="30">
         <f t="shared" si="4"/>
         <v>0.95</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="30">
         <f>_xlfn.XLOOKUP(A7, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="30">
         <f t="shared" si="5"/>
         <v>0.95</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A8, User_Responses!$G$2:$G$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A8, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>5.681818181818183E-2</v>
-      </c>
-      <c r="D8" s="25">
+        <v>5.7142857142857169E-2</v>
+      </c>
+      <c r="D8" s="30">
         <f>_xlfn.XLOOKUP(A8, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="31">
         <f t="shared" si="0"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="30">
         <f>_xlfn.XLOOKUP(A8, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="30">
         <f t="shared" si="1"/>
         <v>0.68333333333333335</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="30">
         <f>_xlfn.XLOOKUP(A8, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="30">
         <f t="shared" si="2"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="30">
         <f>_xlfn.XLOOKUP(A8, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="30">
         <f t="shared" si="3"/>
         <v>0.88333333333333341</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="30">
         <f>_xlfn.XLOOKUP(A8, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="30">
         <f t="shared" si="4"/>
         <v>0.88333333333333341</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="30">
         <f>_xlfn.XLOOKUP(A8, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="30">
         <f t="shared" si="5"/>
         <v>0.88333333333333341</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A9, User_Responses!$G$2:$G$66)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A9, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>5.681818181818183E-2</v>
-      </c>
-      <c r="D9" s="25">
+        <v>5.7142857142857169E-2</v>
+      </c>
+      <c r="D9" s="30">
         <f>_xlfn.XLOOKUP(A9, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="31">
         <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="30">
         <f>_xlfn.XLOOKUP(A9, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="30">
         <f t="shared" si="1"/>
         <v>0.76666666666666661</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="30">
         <f>_xlfn.XLOOKUP(A9, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>1</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="30">
         <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="30">
         <f>_xlfn.XLOOKUP(A9, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.9</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="30">
         <f t="shared" si="3"/>
         <v>0.76666666666666661</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="30">
         <f>_xlfn.XLOOKUP(A9, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="30">
         <f t="shared" si="4"/>
         <v>0.96666666666666667</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="30">
         <f>_xlfn.XLOOKUP(A9, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O9" s="25">
+      <c r="O9" s="30">
         <f t="shared" si="5"/>
         <v>0.86666666666666659</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A10, User_Responses!$G$2:$G$66)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A10, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>4.5454545454545463E-2</v>
-      </c>
-      <c r="D10" s="25">
+        <v>4.5714285714285742E-2</v>
+      </c>
+      <c r="D10" s="30">
         <f>_xlfn.XLOOKUP(A10, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="31">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="30">
         <f>_xlfn.XLOOKUP(A10, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="30">
         <f t="shared" si="1"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="30">
         <f>_xlfn.XLOOKUP(A10, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.9</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="30">
         <f t="shared" si="2"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="30">
         <f>_xlfn.XLOOKUP(A10, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.9</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="30">
         <f t="shared" si="3"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="30">
         <f>_xlfn.XLOOKUP(A10, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="30">
         <f t="shared" si="4"/>
         <v>0.86666666666666659</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="30">
         <f>_xlfn.XLOOKUP(A10, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O10" s="30">
         <f t="shared" si="5"/>
         <v>0.96666666666666667</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A11, User_Responses!$G$2:$G$66)</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A11, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>5.681818181818183E-2</v>
-      </c>
-      <c r="D11" s="25">
+        <v>5.7142857142857169E-2</v>
+      </c>
+      <c r="D11" s="30">
         <f>_xlfn.XLOOKUP(A11, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="31">
         <f t="shared" si="0"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="30">
         <f>_xlfn.XLOOKUP(A11, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="30">
         <f t="shared" si="1"/>
         <v>0.68333333333333335</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="30">
         <f>_xlfn.XLOOKUP(A11, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.9</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="30">
         <f t="shared" si="2"/>
         <v>0.68333333333333335</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="30">
         <f>_xlfn.XLOOKUP(A11, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.8</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="30">
         <f t="shared" si="3"/>
         <v>0.78333333333333333</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="30">
         <f>_xlfn.XLOOKUP(A11, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.8</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="30">
         <f t="shared" si="4"/>
         <v>0.78333333333333333</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="30">
         <f>_xlfn.XLOOKUP(A11, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="30">
         <f t="shared" si="5"/>
         <v>0.78333333333333333</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A12, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A12, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>7.3863636363636381E-2</v>
-      </c>
-      <c r="D12" s="25">
+        <v>7.428571428571433E-2</v>
+      </c>
+      <c r="D12" s="30">
         <f>_xlfn.XLOOKUP(A12, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.5</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="30">
         <f>_xlfn.XLOOKUP(A12, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.6</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="30">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="30">
         <f>_xlfn.XLOOKUP(A12, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="30">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="30">
         <f>_xlfn.XLOOKUP(A12, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="30">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="30">
         <f>_xlfn.XLOOKUP(A12, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="30">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="30">
         <f>_xlfn.XLOOKUP(A12, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.5</v>
       </c>
-      <c r="O12" s="25">
+      <c r="O12" s="30">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A13, User_Responses!$G$2:$G$66)</f>
         <v>1</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A13, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>3.0303030303030307E-2</v>
-      </c>
-      <c r="D13" s="25">
+        <v>3.0476190476190497E-2</v>
+      </c>
+      <c r="D13" s="30">
         <f>_xlfn.XLOOKUP(A13, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.9</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="31">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="30">
         <f>_xlfn.XLOOKUP(A13, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="30">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="30">
         <f>_xlfn.XLOOKUP(A13, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="30">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="30">
         <f>_xlfn.XLOOKUP(A13, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="30">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="30">
         <f>_xlfn.XLOOKUP(A13, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="30">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="30">
         <f>_xlfn.XLOOKUP(A13, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="30">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A14, User_Responses!$G$2:$G$66)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A14, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>2.6515151515151519E-2</v>
-      </c>
-      <c r="D14" s="25">
+        <v>2.6666666666666686E-2</v>
+      </c>
+      <c r="D14" s="30">
         <f>_xlfn.XLOOKUP(A14, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.8</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="31">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="30">
         <f>_xlfn.XLOOKUP(A14, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.8</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="30">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="30">
         <f>_xlfn.XLOOKUP(A14, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.9</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="30">
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="30">
         <f>_xlfn.XLOOKUP(A14, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.8</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="30">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="30">
         <f>_xlfn.XLOOKUP(A14, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="30">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="30">
         <f>_xlfn.XLOOKUP(A14, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="30">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A15, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A15, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>7.5757575757575768E-3</v>
-      </c>
-      <c r="D15" s="25">
+        <v>7.6190476190476242E-3</v>
+      </c>
+      <c r="D15" s="30">
         <f>_xlfn.XLOOKUP(A15, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.9</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="31">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="30">
         <f>_xlfn.XLOOKUP(A15, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="30">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="30">
         <f>_xlfn.XLOOKUP(A15, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="30">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="30">
         <f>_xlfn.XLOOKUP(A15, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>1</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="30">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="30">
         <f>_xlfn.XLOOKUP(A15, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="30">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="30">
         <f>_xlfn.XLOOKUP(A15, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="30">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A16, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A16, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>3.4090909090909095E-2</v>
-      </c>
-      <c r="D16" s="25">
+        <v>3.4285714285714308E-2</v>
+      </c>
+      <c r="D16" s="30">
         <f>_xlfn.XLOOKUP(A16, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.8</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="31">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="30">
         <f>_xlfn.XLOOKUP(A16, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="30">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="30">
         <f>_xlfn.XLOOKUP(A16, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="30">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="30">
         <f>_xlfn.XLOOKUP(A16, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>1</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="30">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="30">
         <f>_xlfn.XLOOKUP(A16, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.8</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="30">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="30">
         <f>_xlfn.XLOOKUP(A16, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="30">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A17, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A17, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>5.6818181818181828E-3</v>
-      </c>
-      <c r="D17" s="25">
+        <v>5.7142857142857178E-3</v>
+      </c>
+      <c r="D17" s="30">
         <f>_xlfn.XLOOKUP(A17, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.6</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="31">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="30">
         <f>_xlfn.XLOOKUP(A17, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.7</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="30">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="30">
         <f>_xlfn.XLOOKUP(A17, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="30">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="30">
         <f>_xlfn.XLOOKUP(A17, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.9</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="30">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="30">
         <f>_xlfn.XLOOKUP(A17, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="30">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="30">
         <f>_xlfn.XLOOKUP(A17, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="30">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A18, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A18, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>3.4090909090909095E-2</v>
-      </c>
-      <c r="D18" s="25">
+        <v>3.4285714285714308E-2</v>
+      </c>
+      <c r="D18" s="30">
         <f>_xlfn.XLOOKUP(A18, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.9</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="31">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="30">
         <f>_xlfn.XLOOKUP(A18, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="30">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="30">
         <f>_xlfn.XLOOKUP(A18, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.9</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="30">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="30">
         <f>_xlfn.XLOOKUP(A18, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.8</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="30">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="L18" s="25">
+      <c r="L18" s="30">
         <f>_xlfn.XLOOKUP(A18, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.8</v>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="30">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="30">
         <f>_xlfn.XLOOKUP(A18, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="30">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A19, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A19, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>2.6515151515151519E-2</v>
-      </c>
-      <c r="D19" s="25">
+        <v>2.6666666666666686E-2</v>
+      </c>
+      <c r="D19" s="30">
         <f>_xlfn.XLOOKUP(A19, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="31">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="30">
         <f>_xlfn.XLOOKUP(A19, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="30">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="30">
         <f>_xlfn.XLOOKUP(A19, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>1</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="30">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="30">
         <f>_xlfn.XLOOKUP(A19, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="30">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="L19" s="25">
+      <c r="L19" s="30">
         <f>_xlfn.XLOOKUP(A19, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.6</v>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="30">
         <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
-      <c r="N19" s="25">
+      <c r="N19" s="30">
         <f>_xlfn.XLOOKUP(A19, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O19" s="25">
+      <c r="O19" s="30">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A20, User_Responses!$G$2:$G$66)</f>
         <v>0.5</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A20, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>1.1363636363636366E-2</v>
-      </c>
-      <c r="D20" s="25">
+        <v>1.1428571428571436E-2</v>
+      </c>
+      <c r="D20" s="30">
         <f>_xlfn.XLOOKUP(A20, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="31">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="30">
         <f>_xlfn.XLOOKUP(A20, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="30">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="30">
         <f>_xlfn.XLOOKUP(A20, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>1</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="30">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="30">
         <f>_xlfn.XLOOKUP(A20, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.7</v>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="30">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="30">
         <f>_xlfn.XLOOKUP(A20, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.7</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="30">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="30">
         <f>_xlfn.XLOOKUP(A20, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.8</v>
       </c>
-      <c r="O20" s="25">
+      <c r="O20" s="30">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A21, User_Responses!$G$2:$G$66)</f>
         <v>0.75</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A21, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>1.8939393939393943E-2</v>
-      </c>
-      <c r="D21" s="25">
+        <v>1.904761904761906E-2</v>
+      </c>
+      <c r="D21" s="30">
         <f>_xlfn.XLOOKUP(A21, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>0.8</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="31">
         <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="30">
         <f>_xlfn.XLOOKUP(A21, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="30">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="30">
         <f>_xlfn.XLOOKUP(A21, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="30">
         <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="30">
         <f>_xlfn.XLOOKUP(A21, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.8</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="30">
         <f t="shared" si="3"/>
         <v>0.95</v>
       </c>
-      <c r="L21" s="25">
+      <c r="L21" s="30">
         <f>_xlfn.XLOOKUP(A21, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.9</v>
       </c>
-      <c r="M21" s="25">
+      <c r="M21" s="30">
         <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
-      <c r="N21" s="25">
+      <c r="N21" s="30">
         <f>_xlfn.XLOOKUP(A21, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.7</v>
       </c>
-      <c r="O21" s="25">
+      <c r="O21" s="30">
         <f t="shared" si="5"/>
         <v>0.95</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="30">
         <f>AVERAGEIF(User_Responses!$B$2:$B$66, A22, User_Responses!$G$2:$G$66)</f>
         <v>0.75</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="30">
         <f>SUMIF(User_Responses!$B$2:$B$66, A22, User_Responses!$H$2:$H$66) / SUM(User_Responses!H$2:$H$66)</f>
-        <v>3.4090909090909095E-2</v>
-      </c>
-      <c r="D22" s="25">
+        <v>3.4285714285714308E-2</v>
+      </c>
+      <c r="D22" s="30">
         <f>_xlfn.XLOOKUP(A22, Platform_DB!$B$1:$Z$1, Platform_DB!$B$2:$Z$2)</f>
         <v>1</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="31">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="30">
         <f>_xlfn.XLOOKUP(A22, Platform_DB!$B$1:$Z$1, Platform_DB!$B$3:$Z$3)</f>
         <v>0.9</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="30">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="30">
         <f>_xlfn.XLOOKUP(A22, Platform_DB!$B$1:$Z$1, Platform_DB!$B$4:$Z$4)</f>
         <v>0.8</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="30">
         <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="30">
         <f>_xlfn.XLOOKUP(A22, Platform_DB!$B$1:$Z$1, Platform_DB!$B$5:$Z$5)</f>
         <v>0.6</v>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="30">
         <f t="shared" si="3"/>
         <v>0.85</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="30">
         <f>_xlfn.XLOOKUP(A22, Platform_DB!$B$1:$Z$1, Platform_DB!$B$6:$Z$6)</f>
         <v>0.6</v>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="30">
         <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="30">
         <f>_xlfn.XLOOKUP(A22, Platform_DB!$B$1:$Z$1, Platform_DB!$B$7:$Z$7)</f>
         <v>0.6</v>
       </c>
-      <c r="O22" s="25">
+      <c r="O22" s="30">
         <f t="shared" si="5"/>
         <v>0.85</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="23" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="32">
         <f>SUMPRODUCT($C$2:$C$21, E2:E21)</f>
-        <v>0.59318181818181837</v>
-      </c>
-      <c r="E25" s="29">
+        <v>0.59628571428571453</v>
+      </c>
+      <c r="E25" s="32">
         <f>SUMPRODUCT($C$2:$C$21, G2:G21)</f>
-        <v>0.58806818181818199</v>
-      </c>
-      <c r="F25" s="29">
+        <v>0.59171428571428608</v>
+      </c>
+      <c r="F25" s="32">
         <f>SUMPRODUCT($C$2:$C$21, I2:I21)</f>
-        <v>0.59810606060606064</v>
-      </c>
-      <c r="G25" s="27">
+        <v>0.60238095238095257</v>
+      </c>
+      <c r="G25" s="31">
         <f>SUMPRODUCT($C$2:$C$21, K2:K21)</f>
-        <v>0.64356060606060617</v>
-      </c>
-      <c r="H25" s="29">
+        <v>0.64866666666666684</v>
+      </c>
+      <c r="H25" s="32">
         <f>SUMPRODUCT($C$2:$C$21, M2:M21)</f>
-        <v>0.68219696969696986</v>
-      </c>
-      <c r="I25" s="27">
+        <v>0.67533333333333379</v>
+      </c>
+      <c r="I25" s="31">
         <f>SUMPRODUCT($C$2:$C$21, O2:O21)</f>
-        <v>0.70018939393939394</v>
-      </c>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
+        <v>0.70447619047619081</v>
+      </c>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C30" s="26"/>
+      <c r="C30" s="22"/>
+    </row>
+    <row r="58" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="33" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="ts2WNs7DX+2fFM7vZ5pT8I83LyOE4aMjDfGRICzaFfnQGyB+S43qBiGuIKzdmSgpYYc6lNcYQQ8Dm7tJaGVa/Q==" saltValue="43cIDFL3Drd1lVPogAUkrw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
